--- a/Avaliações dos Itens/Avaliações (2008-2024)/2020 nível 1 tipo A.xlsx
+++ b/Avaliações dos Itens/Avaliações (2008-2024)/2020 nível 1 tipo A.xlsx
@@ -2,13 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1a040bb1f01841a5/Desktop/Educomp 2026/Análises/Avaliação 1/criterios por questoes e provas/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="8_{87E6E89C-60CF-4AF5-952C-B684069F8989}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E42428FB-5092-472E-90D5-BAC2FA57F099}"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{87E6E89C-60CF-4AF5-952C-B684069F8989}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{503E1C13-1B22-4695-93FB-F7E4DD84A73D}"/>
   <bookViews>
     <workbookView xWindow="29388" yWindow="-81" windowWidth="29698" windowHeight="16094" xr2:uid="{23B7687B-E1D9-4F15-B7DA-81C3367EAFE7}"/>
   </bookViews>
@@ -152,10 +147,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -658,12 +649,90 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="1"/>
-      <c r="B98" s="2"/>
-      <c r="C98" s="2"/>
-    </row>
+    <row r="17" x14ac:dyDescent="0.3"/>
+    <row r="18" x14ac:dyDescent="0.3"/>
+    <row r="19" x14ac:dyDescent="0.3"/>
+    <row r="20" x14ac:dyDescent="0.3"/>
+    <row r="21" x14ac:dyDescent="0.3"/>
+    <row r="22" x14ac:dyDescent="0.3"/>
+    <row r="23" x14ac:dyDescent="0.3"/>
+    <row r="24" x14ac:dyDescent="0.3"/>
+    <row r="25" x14ac:dyDescent="0.3"/>
+    <row r="26" x14ac:dyDescent="0.3"/>
+    <row r="27" x14ac:dyDescent="0.3"/>
+    <row r="28" x14ac:dyDescent="0.3"/>
+    <row r="29" x14ac:dyDescent="0.3"/>
+    <row r="30" x14ac:dyDescent="0.3"/>
+    <row r="31" x14ac:dyDescent="0.3"/>
+    <row r="32" x14ac:dyDescent="0.3"/>
+    <row r="33" x14ac:dyDescent="0.3"/>
+    <row r="34" x14ac:dyDescent="0.3"/>
+    <row r="35" x14ac:dyDescent="0.3"/>
+    <row r="36" x14ac:dyDescent="0.3"/>
+    <row r="37" x14ac:dyDescent="0.3"/>
+    <row r="38" x14ac:dyDescent="0.3"/>
+    <row r="39" x14ac:dyDescent="0.3"/>
+    <row r="40" x14ac:dyDescent="0.3"/>
+    <row r="41" x14ac:dyDescent="0.3"/>
+    <row r="42" x14ac:dyDescent="0.3"/>
+    <row r="43" x14ac:dyDescent="0.3"/>
+    <row r="44" x14ac:dyDescent="0.3"/>
+    <row r="45" x14ac:dyDescent="0.3"/>
+    <row r="46" x14ac:dyDescent="0.3"/>
+    <row r="47" x14ac:dyDescent="0.3"/>
+    <row r="48" x14ac:dyDescent="0.3"/>
+    <row r="49" x14ac:dyDescent="0.3"/>
+    <row r="50" x14ac:dyDescent="0.3"/>
+    <row r="51" x14ac:dyDescent="0.3"/>
+    <row r="52" x14ac:dyDescent="0.3"/>
+    <row r="53" x14ac:dyDescent="0.3"/>
+    <row r="54" x14ac:dyDescent="0.3"/>
+    <row r="55" x14ac:dyDescent="0.3"/>
+    <row r="56" x14ac:dyDescent="0.3"/>
+    <row r="57" x14ac:dyDescent="0.3"/>
+    <row r="58" x14ac:dyDescent="0.3"/>
+    <row r="59" x14ac:dyDescent="0.3"/>
+    <row r="60" x14ac:dyDescent="0.3"/>
+    <row r="61" x14ac:dyDescent="0.3"/>
+    <row r="62" x14ac:dyDescent="0.3"/>
+    <row r="63" x14ac:dyDescent="0.3"/>
+    <row r="64" x14ac:dyDescent="0.3"/>
+    <row r="65" x14ac:dyDescent="0.3"/>
+    <row r="66" x14ac:dyDescent="0.3"/>
+    <row r="67" x14ac:dyDescent="0.3"/>
+    <row r="68" x14ac:dyDescent="0.3"/>
+    <row r="69" x14ac:dyDescent="0.3"/>
+    <row r="70" x14ac:dyDescent="0.3"/>
+    <row r="71" x14ac:dyDescent="0.3"/>
+    <row r="72" x14ac:dyDescent="0.3"/>
+    <row r="73" x14ac:dyDescent="0.3"/>
+    <row r="74" x14ac:dyDescent="0.3"/>
+    <row r="75" x14ac:dyDescent="0.3"/>
+    <row r="76" x14ac:dyDescent="0.3"/>
+    <row r="77" x14ac:dyDescent="0.3"/>
+    <row r="78" x14ac:dyDescent="0.3"/>
+    <row r="79" x14ac:dyDescent="0.3"/>
+    <row r="80" x14ac:dyDescent="0.3"/>
+    <row r="81" x14ac:dyDescent="0.3"/>
+    <row r="82" x14ac:dyDescent="0.3"/>
+    <row r="83" x14ac:dyDescent="0.3"/>
+    <row r="84" x14ac:dyDescent="0.3"/>
+    <row r="85" x14ac:dyDescent="0.3"/>
+    <row r="86" x14ac:dyDescent="0.3"/>
+    <row r="87" x14ac:dyDescent="0.3"/>
+    <row r="88" x14ac:dyDescent="0.3"/>
+    <row r="89" x14ac:dyDescent="0.3"/>
+    <row r="90" x14ac:dyDescent="0.3"/>
+    <row r="91" x14ac:dyDescent="0.3"/>
+    <row r="92" x14ac:dyDescent="0.3"/>
+    <row r="93" x14ac:dyDescent="0.3"/>
+    <row r="94" x14ac:dyDescent="0.3"/>
+    <row r="95" x14ac:dyDescent="0.3"/>
+    <row r="96" x14ac:dyDescent="0.3"/>
+    <row r="97" x14ac:dyDescent="0.3"/>
+    <row r="98" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>